--- a/excel/02_medicacion.xlsx
+++ b/excel/02_medicacion.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,19 +413,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1667"/>
+  <dimension ref="A1:F1757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
@@ -8892,8 +8888,10 @@
           <t>URSOMARINA</t>
         </is>
       </c>
-      <c r="D265" t="n">
-        <v>10</v>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -9050,8 +9048,10 @@
           <t>URSOMARINA</t>
         </is>
       </c>
-      <c r="D270" t="n">
-        <v>10</v>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -9208,8 +9208,10 @@
           <t>URSOMARINA</t>
         </is>
       </c>
-      <c r="D275" t="n">
-        <v>10</v>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -9366,8 +9368,10 @@
           <t>URSOMARINA</t>
         </is>
       </c>
-      <c r="D280" t="n">
-        <v>10</v>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -9524,8 +9528,10 @@
           <t>URSOMARINA</t>
         </is>
       </c>
-      <c r="D285" t="n">
-        <v>10</v>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -9682,8 +9688,10 @@
           <t>URSOMARINA</t>
         </is>
       </c>
-      <c r="D290" t="n">
-        <v>10</v>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -9840,8 +9848,10 @@
           <t>URSOMARINA</t>
         </is>
       </c>
-      <c r="D295" t="n">
-        <v>10</v>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -13490,8 +13500,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D410" t="n">
-        <v>0.1</v>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
@@ -13680,8 +13692,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D416" t="n">
-        <v>0.1</v>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
@@ -13870,8 +13884,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D422" t="n">
-        <v>0.1</v>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
@@ -14060,8 +14076,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D428" t="n">
-        <v>0.1</v>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
@@ -14250,8 +14268,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D434" t="n">
-        <v>0.1</v>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
@@ -14440,8 +14460,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D440" t="n">
-        <v>0.1</v>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
@@ -14630,8 +14652,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D446" t="n">
-        <v>0.1</v>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
@@ -14820,8 +14844,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D452" t="n">
-        <v>0.1</v>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
@@ -15010,8 +15036,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D458" t="n">
-        <v>0.08</v>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
@@ -15200,8 +15228,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D464" t="n">
-        <v>0.1</v>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
@@ -15390,8 +15420,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D470" t="n">
-        <v>0.1</v>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
@@ -15580,8 +15612,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D476" t="n">
-        <v>0.1</v>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
@@ -15770,8 +15804,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D482" t="n">
-        <v>0.1</v>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
@@ -15960,8 +15996,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D488" t="n">
-        <v>0.1</v>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
@@ -17082,8 +17120,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D524" t="n">
-        <v>0.12</v>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
@@ -17112,8 +17152,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D525" t="n">
-        <v>0.12</v>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
@@ -17142,8 +17184,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D526" t="n">
-        <v>0.14</v>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
@@ -17172,8 +17216,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D527" t="n">
-        <v>0.14</v>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
@@ -17202,8 +17248,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D528" t="n">
-        <v>0.16</v>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
@@ -17232,8 +17280,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D529" t="n">
-        <v>0.14</v>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
@@ -17262,8 +17312,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D530" t="n">
-        <v>0.16</v>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
@@ -17548,8 +17600,10 @@
           <t>MELOXICAM</t>
         </is>
       </c>
-      <c r="D539" t="n">
-        <v>0.1</v>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
@@ -17578,8 +17632,10 @@
           <t>MELOXICAM</t>
         </is>
       </c>
-      <c r="D540" t="n">
-        <v>0.1</v>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
@@ -17608,8 +17664,10 @@
           <t>MELOXICAM</t>
         </is>
       </c>
-      <c r="D541" t="n">
-        <v>0.1</v>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
@@ -17638,8 +17696,10 @@
           <t>MELOXICAM</t>
         </is>
       </c>
-      <c r="D542" t="n">
-        <v>0.1</v>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
@@ -17668,8 +17728,10 @@
           <t>MELOXICAM</t>
         </is>
       </c>
-      <c r="D543" t="n">
-        <v>0.1</v>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
@@ -17698,8 +17760,10 @@
           <t>MELOXICAM</t>
         </is>
       </c>
-      <c r="D544" t="n">
-        <v>0.1</v>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
@@ -18624,8 +18688,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D573" t="n">
-        <v>0.12</v>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
@@ -18654,8 +18720,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D574" t="n">
-        <v>0.14</v>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
@@ -18684,8 +18752,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D575" t="n">
-        <v>0.14</v>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
@@ -18714,8 +18784,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D576" t="n">
-        <v>0.16</v>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
@@ -18744,8 +18816,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D577" t="n">
-        <v>0.14</v>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
@@ -18774,8 +18848,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D578" t="n">
-        <v>0.16</v>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
@@ -18804,8 +18880,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D579" t="n">
-        <v>0.16</v>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
@@ -20374,8 +20452,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D629" t="n">
-        <v>0.16</v>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
@@ -20404,8 +20484,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D630" t="n">
-        <v>0.16</v>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
@@ -20434,8 +20516,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D631" t="n">
-        <v>0.16</v>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
@@ -20464,8 +20548,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D632" t="n">
-        <v>0.16</v>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
@@ -20494,8 +20580,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D633" t="n">
-        <v>0.2</v>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
@@ -20524,8 +20612,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D634" t="n">
-        <v>0.2</v>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
@@ -20554,8 +20644,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D635" t="n">
-        <v>0.2</v>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
@@ -21704,8 +21796,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D671" t="n">
-        <v>0.16</v>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
@@ -21734,8 +21828,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D672" t="n">
-        <v>0.16</v>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
@@ -21764,8 +21860,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D673" t="n">
-        <v>0.16</v>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
@@ -21794,8 +21892,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D674" t="n">
-        <v>0.2</v>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
@@ -21824,8 +21924,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D675" t="n">
-        <v>0.2</v>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
@@ -21854,8 +21956,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D676" t="n">
-        <v>0.2</v>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
@@ -21884,8 +21988,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D677" t="n">
-        <v>0.2</v>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
@@ -24702,8 +24808,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D766" t="n">
-        <v>0.22</v>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E766" t="inlineStr">
         <is>
@@ -24860,8 +24968,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D771" t="n">
-        <v>0.22</v>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E771" t="inlineStr">
         <is>
@@ -25018,8 +25128,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D776" t="n">
-        <v>0.22</v>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E776" t="inlineStr">
         <is>
@@ -25176,8 +25288,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D781" t="n">
-        <v>0.22</v>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E781" t="inlineStr">
         <is>
@@ -25334,8 +25448,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D786" t="n">
-        <v>0.22</v>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E786" t="inlineStr">
         <is>
@@ -25492,8 +25608,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D791" t="n">
-        <v>0.22</v>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E791" t="inlineStr">
         <is>
@@ -25650,8 +25768,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D796" t="n">
-        <v>0.22</v>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E796" t="inlineStr">
         <is>
@@ -25808,8 +25928,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D801" t="n">
-        <v>0.22</v>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E801" t="inlineStr">
         <is>
@@ -25966,8 +26088,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D806" t="n">
-        <v>0.22</v>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E806" t="inlineStr">
         <is>
@@ -26124,8 +26248,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D811" t="n">
-        <v>0.22</v>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E811" t="inlineStr">
         <is>
@@ -26282,8 +26408,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D816" t="n">
-        <v>0.22</v>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E816" t="inlineStr">
         <is>
@@ -26440,8 +26568,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D821" t="n">
-        <v>0.22</v>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E821" t="inlineStr">
         <is>
@@ -26598,8 +26728,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D826" t="n">
-        <v>0.22</v>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E826" t="inlineStr">
         <is>
@@ -26756,8 +26888,10 @@
           <t>INSULINA</t>
         </is>
       </c>
-      <c r="D831" t="n">
-        <v>0.22</v>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E831" t="inlineStr">
         <is>
@@ -26910,8 +27044,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D836" t="n">
-        <v>0.22</v>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E836" t="inlineStr">
         <is>
@@ -27036,8 +27172,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D840" t="n">
-        <v>0.22</v>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E840" t="inlineStr">
         <is>
@@ -27190,8 +27328,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D845" t="n">
-        <v>0.22</v>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E845" t="inlineStr">
         <is>
@@ -27316,8 +27456,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D849" t="n">
-        <v>0.22</v>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E849" t="inlineStr">
         <is>
@@ -27470,8 +27612,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D854" t="n">
-        <v>0.22</v>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E854" t="inlineStr">
         <is>
@@ -27596,8 +27740,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D858" t="n">
-        <v>0.22</v>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E858" t="inlineStr">
         <is>
@@ -27750,8 +27896,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D863" t="n">
-        <v>0.22</v>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E863" t="inlineStr">
         <is>
@@ -27876,8 +28024,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D867" t="n">
-        <v>0.22</v>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E867" t="inlineStr">
         <is>
@@ -28030,8 +28180,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D872" t="n">
-        <v>0.22</v>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E872" t="inlineStr">
         <is>
@@ -28156,8 +28308,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D876" t="n">
-        <v>0.22</v>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E876" t="inlineStr">
         <is>
@@ -28310,8 +28464,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D881" t="n">
-        <v>0.22</v>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E881" t="inlineStr">
         <is>
@@ -28436,8 +28592,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D885" t="n">
-        <v>0.22</v>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E885" t="inlineStr">
         <is>
@@ -28590,8 +28748,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D890" t="n">
-        <v>0.22</v>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E890" t="inlineStr">
         <is>
@@ -28716,8 +28876,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D894" t="n">
-        <v>0.22</v>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E894" t="inlineStr">
         <is>
@@ -28838,8 +29000,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D898" t="n">
-        <v>0.22</v>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E898" t="inlineStr">
         <is>
@@ -28932,8 +29096,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D901" t="n">
-        <v>0.22</v>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E901" t="inlineStr">
         <is>
@@ -29146,8 +29312,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D908" t="n">
-        <v>0.22</v>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E908" t="inlineStr">
         <is>
@@ -29268,8 +29436,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D912" t="n">
-        <v>0.22</v>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E912" t="inlineStr">
         <is>
@@ -29362,8 +29532,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D915" t="n">
-        <v>0.22</v>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E915" t="inlineStr">
         <is>
@@ -29484,8 +29656,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D919" t="n">
-        <v>0.22</v>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E919" t="inlineStr">
         <is>
@@ -29578,8 +29752,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D922" t="n">
-        <v>0.22</v>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E922" t="inlineStr">
         <is>
@@ -29700,8 +29876,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D926" t="n">
-        <v>0.22</v>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E926" t="inlineStr">
         <is>
@@ -29794,8 +29972,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D929" t="n">
-        <v>0.22</v>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E929" t="inlineStr">
         <is>
@@ -29916,8 +30096,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D933" t="n">
-        <v>0.22</v>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E933" t="inlineStr">
         <is>
@@ -30010,8 +30192,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D936" t="n">
-        <v>0.22</v>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E936" t="inlineStr">
         <is>
@@ -30132,8 +30316,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D940" t="n">
-        <v>0.22</v>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E940" t="inlineStr">
         <is>
@@ -30226,8 +30412,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D943" t="n">
-        <v>0.22</v>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E943" t="inlineStr">
         <is>
@@ -30544,8 +30732,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D953" t="n">
-        <v>0.22</v>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E953" t="inlineStr">
         <is>
@@ -30634,8 +30824,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D956" t="n">
-        <v>0.22</v>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E956" t="inlineStr">
         <is>
@@ -30760,8 +30952,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D960" t="n">
-        <v>0.22</v>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E960" t="inlineStr">
         <is>
@@ -30850,8 +31044,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D963" t="n">
-        <v>0.22</v>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E963" t="inlineStr">
         <is>
@@ -30976,8 +31172,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D967" t="n">
-        <v>0.22</v>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E967" t="inlineStr">
         <is>
@@ -31066,8 +31264,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D970" t="n">
-        <v>0.22</v>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E970" t="inlineStr">
         <is>
@@ -31192,8 +31392,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D974" t="n">
-        <v>0.22</v>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E974" t="inlineStr">
         <is>
@@ -31282,8 +31484,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D977" t="n">
-        <v>0.22</v>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E977" t="inlineStr">
         <is>
@@ -31408,8 +31612,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D981" t="n">
-        <v>0.22</v>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E981" t="inlineStr">
         <is>
@@ -31498,8 +31704,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D984" t="n">
-        <v>0.22</v>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E984" t="inlineStr">
         <is>
@@ -31624,8 +31832,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D988" t="n">
-        <v>0.22</v>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E988" t="inlineStr">
         <is>
@@ -31714,8 +31924,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D991" t="n">
-        <v>0.22</v>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E991" t="inlineStr">
         <is>
@@ -31840,8 +32052,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D995" t="n">
-        <v>0.22</v>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E995" t="inlineStr">
         <is>
@@ -31930,8 +32144,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D998" t="n">
-        <v>0.22</v>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="E998" t="inlineStr">
         <is>
@@ -32052,8 +32268,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1002" t="n">
-        <v>0.22</v>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1002" t="inlineStr">
         <is>
@@ -32114,8 +32332,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1004" t="n">
-        <v>0.22</v>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1004" t="inlineStr">
         <is>
@@ -32268,8 +32488,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1009" t="n">
-        <v>0.24</v>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1009" t="inlineStr">
         <is>
@@ -32330,8 +32552,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1011" t="n">
-        <v>0.22</v>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1011" t="inlineStr">
         <is>
@@ -32484,8 +32708,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1016" t="n">
-        <v>0.24</v>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1016" t="inlineStr">
         <is>
@@ -32546,8 +32772,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1018" t="n">
-        <v>0.22</v>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1018" t="inlineStr">
         <is>
@@ -32700,8 +32928,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1023" t="n">
-        <v>0.24</v>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1023" t="inlineStr">
         <is>
@@ -32762,8 +32992,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1025" t="n">
-        <v>0.22</v>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1025" t="inlineStr">
         <is>
@@ -32916,8 +33148,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1030" t="n">
-        <v>0.24</v>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1030" t="inlineStr">
         <is>
@@ -32978,8 +33212,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1032" t="n">
-        <v>0.22</v>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1032" t="inlineStr">
         <is>
@@ -33132,8 +33368,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1037" t="n">
-        <v>0.24</v>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1037" t="inlineStr">
         <is>
@@ -33194,8 +33432,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1039" t="n">
-        <v>0.22</v>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1039" t="inlineStr">
         <is>
@@ -33348,8 +33588,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1044" t="n">
-        <v>0.24</v>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1044" t="inlineStr">
         <is>
@@ -33410,8 +33652,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1046" t="n">
-        <v>0.22</v>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1046" t="inlineStr">
         <is>
@@ -33568,8 +33812,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1051" t="n">
-        <v>0.24</v>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1051" t="inlineStr">
         <is>
@@ -33662,8 +33908,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1054" t="n">
-        <v>0.22</v>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1054" t="inlineStr">
         <is>
@@ -33756,8 +34004,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1057" t="n">
-        <v>0.24</v>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1057" t="inlineStr">
         <is>
@@ -33850,8 +34100,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1060" t="n">
-        <v>0.22</v>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1060" t="inlineStr">
         <is>
@@ -33944,8 +34196,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1063" t="n">
-        <v>0.24</v>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1063" t="inlineStr">
         <is>
@@ -34038,8 +34292,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1066" t="n">
-        <v>0.24</v>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1066" t="inlineStr">
         <is>
@@ -34132,8 +34388,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1069" t="n">
-        <v>0.24</v>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1069" t="inlineStr">
         <is>
@@ -34226,8 +34484,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1072" t="n">
-        <v>0.24</v>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1072" t="inlineStr">
         <is>
@@ -34320,8 +34580,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1075" t="n">
-        <v>0.24</v>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1075" t="inlineStr">
         <is>
@@ -34414,8 +34676,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1078" t="n">
-        <v>0.24</v>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1078" t="inlineStr">
         <is>
@@ -34600,8 +34864,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1084" t="n">
-        <v>0.24</v>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1084" t="inlineStr">
         <is>
@@ -34694,8 +34960,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1087" t="n">
-        <v>0.24</v>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1087" t="inlineStr">
         <is>
@@ -34788,8 +35056,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1090" t="n">
-        <v>0.24</v>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1090" t="inlineStr">
         <is>
@@ -34882,8 +35152,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1093" t="n">
-        <v>0.24</v>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1093" t="inlineStr">
         <is>
@@ -34976,8 +35248,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1096" t="n">
-        <v>0.24</v>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1096" t="inlineStr">
         <is>
@@ -35070,8 +35344,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1099" t="n">
-        <v>0.24</v>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1099" t="inlineStr">
         <is>
@@ -35164,8 +35440,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1102" t="n">
-        <v>0.24</v>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1102" t="inlineStr">
         <is>
@@ -35258,8 +35536,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1105" t="n">
-        <v>0.24</v>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1105" t="inlineStr">
         <is>
@@ -35352,8 +35632,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1108" t="n">
-        <v>0.24</v>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1108" t="inlineStr">
         <is>
@@ -35446,8 +35728,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1111" t="n">
-        <v>0.24</v>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1111" t="inlineStr">
         <is>
@@ -35540,8 +35824,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1114" t="n">
-        <v>0.24</v>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1114" t="inlineStr">
         <is>
@@ -35634,8 +35920,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1117" t="n">
-        <v>0.24</v>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1117" t="inlineStr">
         <is>
@@ -35728,8 +36016,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1120" t="n">
-        <v>0.24</v>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1120" t="inlineStr">
         <is>
@@ -35822,8 +36112,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1123" t="n">
-        <v>0.24</v>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1123" t="inlineStr">
         <is>
@@ -35916,8 +36208,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1126" t="n">
-        <v>0.24</v>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1126" t="inlineStr">
         <is>
@@ -36010,8 +36304,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1129" t="n">
-        <v>0.24</v>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1129" t="inlineStr">
         <is>
@@ -36104,8 +36400,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1132" t="n">
-        <v>0.24</v>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1132" t="inlineStr">
         <is>
@@ -36198,8 +36496,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1135" t="n">
-        <v>0.24</v>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1135" t="inlineStr">
         <is>
@@ -36292,8 +36592,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1138" t="n">
-        <v>0.24</v>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1138" t="inlineStr">
         <is>
@@ -36386,8 +36688,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1141" t="n">
-        <v>0.24</v>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1141" t="inlineStr">
         <is>
@@ -36480,8 +36784,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1144" t="n">
-        <v>0.24</v>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1144" t="inlineStr">
         <is>
@@ -36574,8 +36880,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1147" t="n">
-        <v>0.24</v>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1147" t="inlineStr">
         <is>
@@ -36668,8 +36976,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1150" t="n">
-        <v>0.24</v>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1150" t="inlineStr">
         <is>
@@ -36762,8 +37072,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1153" t="n">
-        <v>0.24</v>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1153" t="inlineStr">
         <is>
@@ -36856,8 +37168,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1156" t="n">
-        <v>0.24</v>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1156" t="inlineStr">
         <is>
@@ -36950,8 +37264,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1159" t="n">
-        <v>0.24</v>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1159" t="inlineStr">
         <is>
@@ -37044,8 +37360,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1162" t="n">
-        <v>0.24</v>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1162" t="inlineStr">
         <is>
@@ -37138,8 +37456,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1165" t="n">
-        <v>0.24</v>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1165" t="inlineStr">
         <is>
@@ -37232,8 +37552,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1168" t="n">
-        <v>0.24</v>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1168" t="inlineStr">
         <is>
@@ -37418,8 +37740,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1174" t="n">
-        <v>0.24</v>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1174" t="inlineStr">
         <is>
@@ -37512,8 +37836,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1177" t="n">
-        <v>0.24</v>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1177" t="inlineStr">
         <is>
@@ -37606,8 +37932,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1180" t="n">
-        <v>0.24</v>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1180" t="inlineStr">
         <is>
@@ -37792,8 +38120,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1186" t="n">
-        <v>0.24</v>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1186" t="inlineStr">
         <is>
@@ -37978,8 +38308,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1192" t="n">
-        <v>0.24</v>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1192" t="inlineStr">
         <is>
@@ -38072,8 +38404,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1195" t="n">
-        <v>0.24</v>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1195" t="inlineStr">
         <is>
@@ -38166,8 +38500,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1198" t="n">
-        <v>0.24</v>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1198" t="inlineStr">
         <is>
@@ -38352,8 +38688,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1204" t="n">
-        <v>0.24</v>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1204" t="inlineStr">
         <is>
@@ -38446,8 +38784,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1207" t="n">
-        <v>0.24</v>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1207" t="inlineStr">
         <is>
@@ -38540,8 +38880,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1210" t="n">
-        <v>0.24</v>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1210" t="inlineStr">
         <is>
@@ -38634,8 +38976,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1213" t="n">
-        <v>0.24</v>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1213" t="inlineStr">
         <is>
@@ -38912,8 +39256,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1222" t="n">
-        <v>0.24</v>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1222" t="inlineStr">
         <is>
@@ -39098,8 +39444,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1228" t="n">
-        <v>0.24</v>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1228" t="inlineStr">
         <is>
@@ -39284,8 +39632,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1234" t="n">
-        <v>0.24</v>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1234" t="inlineStr">
         <is>
@@ -39378,8 +39728,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1237" t="n">
-        <v>0.24</v>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1237" t="inlineStr">
         <is>
@@ -39472,8 +39824,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1240" t="n">
-        <v>0.24</v>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1240" t="inlineStr">
         <is>
@@ -39658,8 +40012,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1246" t="n">
-        <v>0.24</v>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1246" t="inlineStr">
         <is>
@@ -40028,8 +40384,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1258" t="n">
-        <v>0.24</v>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1258" t="inlineStr">
         <is>
@@ -40506,8 +40864,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1273" t="n">
-        <v>0.24</v>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1273" t="inlineStr">
         <is>
@@ -40536,8 +40896,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1274" t="n">
-        <v>0.24</v>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1274" t="inlineStr">
         <is>
@@ -40566,8 +40928,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1275" t="n">
-        <v>0.24</v>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1275" t="inlineStr">
         <is>
@@ -40596,8 +40960,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1276" t="n">
-        <v>0.24</v>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1276" t="inlineStr">
         <is>
@@ -40626,8 +40992,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1277" t="n">
-        <v>0.24</v>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1277" t="inlineStr">
         <is>
@@ -40656,8 +41024,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1278" t="n">
-        <v>0.24</v>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1278" t="inlineStr">
         <is>
@@ -40686,8 +41056,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1279" t="n">
-        <v>0.24</v>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1279" t="inlineStr">
         <is>
@@ -41164,8 +41536,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1294" t="n">
-        <v>0.24</v>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1294" t="inlineStr">
         <is>
@@ -41194,8 +41568,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1295" t="n">
-        <v>0.24</v>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1295" t="inlineStr">
         <is>
@@ -41224,8 +41600,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1296" t="n">
-        <v>0.24</v>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1296" t="inlineStr">
         <is>
@@ -41254,8 +41632,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1297" t="n">
-        <v>0.24</v>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1297" t="inlineStr">
         <is>
@@ -41284,8 +41664,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1298" t="n">
-        <v>0.24</v>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1298" t="inlineStr">
         <is>
@@ -41314,8 +41696,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1299" t="n">
-        <v>0.24</v>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1299" t="inlineStr">
         <is>
@@ -41344,8 +41728,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1300" t="n">
-        <v>0.24</v>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1300" t="inlineStr">
         <is>
@@ -41822,8 +42208,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1315" t="n">
-        <v>0.24</v>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1315" t="inlineStr">
         <is>
@@ -41852,8 +42240,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1316" t="n">
-        <v>0.24</v>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1316" t="inlineStr">
         <is>
@@ -41882,8 +42272,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1317" t="n">
-        <v>0.24</v>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1317" t="inlineStr">
         <is>
@@ -41912,8 +42304,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1318" t="n">
-        <v>0.24</v>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1318" t="inlineStr">
         <is>
@@ -41942,8 +42336,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1319" t="n">
-        <v>0.24</v>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1319" t="inlineStr">
         <is>
@@ -41972,8 +42368,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1320" t="n">
-        <v>0.24</v>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1320" t="inlineStr">
         <is>
@@ -42002,8 +42400,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1321" t="n">
-        <v>0.24</v>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
       </c>
       <c r="E1321" t="inlineStr">
         <is>
@@ -42480,8 +42880,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1336" t="n">
-        <v>0.22</v>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1336" t="inlineStr">
         <is>
@@ -42510,8 +42912,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1337" t="n">
-        <v>0.22</v>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1337" t="inlineStr">
         <is>
@@ -42540,8 +42944,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1338" t="n">
-        <v>0.22</v>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1338" t="inlineStr">
         <is>
@@ -42570,8 +42976,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1339" t="n">
-        <v>0.22</v>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1339" t="inlineStr">
         <is>
@@ -42600,8 +43008,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1340" t="n">
-        <v>0.22</v>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1340" t="inlineStr">
         <is>
@@ -42630,8 +43040,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1341" t="n">
-        <v>0.22</v>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1341" t="inlineStr">
         <is>
@@ -42660,8 +43072,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1342" t="n">
-        <v>0.22</v>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1342" t="inlineStr">
         <is>
@@ -43138,8 +43552,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1357" t="n">
-        <v>0.22</v>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1357" t="inlineStr">
         <is>
@@ -43168,8 +43584,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1358" t="n">
-        <v>0.22</v>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1358" t="inlineStr">
         <is>
@@ -43198,8 +43616,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1359" t="n">
-        <v>0.22</v>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1359" t="inlineStr">
         <is>
@@ -43228,8 +43648,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1360" t="n">
-        <v>0.22</v>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1360" t="inlineStr">
         <is>
@@ -43258,8 +43680,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1361" t="n">
-        <v>0.22</v>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1361" t="inlineStr">
         <is>
@@ -43288,8 +43712,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1362" t="n">
-        <v>0.22</v>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1362" t="inlineStr">
         <is>
@@ -43318,8 +43744,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1363" t="n">
-        <v>0.22</v>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1363" t="inlineStr">
         <is>
@@ -44020,8 +44448,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1385" t="n">
-        <v>0.22</v>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1385" t="inlineStr">
         <is>
@@ -44050,8 +44480,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1386" t="n">
-        <v>0.22</v>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1386" t="inlineStr">
         <is>
@@ -44080,8 +44512,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1387" t="n">
-        <v>0.22</v>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1387" t="inlineStr">
         <is>
@@ -44110,8 +44544,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1388" t="n">
-        <v>0.22</v>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1388" t="inlineStr">
         <is>
@@ -44140,8 +44576,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1389" t="n">
-        <v>0.22</v>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1389" t="inlineStr">
         <is>
@@ -44170,8 +44608,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1390" t="n">
-        <v>0.22</v>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1390" t="inlineStr">
         <is>
@@ -44200,8 +44640,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1391" t="n">
-        <v>0.22</v>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1391" t="inlineStr">
         <is>
@@ -44710,8 +45152,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1407" t="n">
-        <v>0.22</v>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1407" t="inlineStr">
         <is>
@@ -44740,8 +45184,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1408" t="n">
-        <v>0.22</v>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1408" t="inlineStr">
         <is>
@@ -44770,8 +45216,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1409" t="n">
-        <v>0.22</v>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1409" t="inlineStr">
         <is>
@@ -44800,8 +45248,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1410" t="n">
-        <v>0.22</v>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1410" t="inlineStr">
         <is>
@@ -44830,8 +45280,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1411" t="n">
-        <v>0.22</v>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1411" t="inlineStr">
         <is>
@@ -44860,8 +45312,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1412" t="n">
-        <v>0.2</v>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
       </c>
       <c r="E1412" t="inlineStr">
         <is>
@@ -44890,8 +45344,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1413" t="n">
-        <v>0.2</v>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
       </c>
       <c r="E1413" t="inlineStr">
         <is>
@@ -45796,8 +46252,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1442" t="n">
-        <v>0.22</v>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1442" t="inlineStr">
         <is>
@@ -45826,8 +46284,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1443" t="n">
-        <v>0.22</v>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
       </c>
       <c r="E1443" t="inlineStr">
         <is>
@@ -45856,8 +46316,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1444" t="n">
-        <v>0.2</v>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>0,20</t>
+        </is>
       </c>
       <c r="E1444" t="inlineStr">
         <is>
@@ -45886,8 +46348,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1445" t="n">
-        <v>0.2</v>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
       </c>
       <c r="E1445" t="inlineStr">
         <is>
@@ -45916,8 +46380,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1446" t="n">
-        <v>0.2</v>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
       </c>
       <c r="E1446" t="inlineStr">
         <is>
@@ -45946,8 +46412,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1447" t="n">
-        <v>0.2</v>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
       </c>
       <c r="E1447" t="inlineStr">
         <is>
@@ -45976,8 +46444,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1448" t="n">
-        <v>0.2</v>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
       </c>
       <c r="E1448" t="inlineStr">
         <is>
@@ -46902,8 +47372,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1477" t="n">
-        <v>0.2</v>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
       </c>
       <c r="E1477" t="inlineStr">
         <is>
@@ -46932,8 +47404,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1478" t="n">
-        <v>0.18</v>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1478" t="inlineStr">
         <is>
@@ -46962,8 +47436,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1479" t="n">
-        <v>0.18</v>
+      <c r="D1479" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1479" t="inlineStr">
         <is>
@@ -46992,8 +47468,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1480" t="n">
-        <v>0.2</v>
+      <c r="D1480" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
       </c>
       <c r="E1480" t="inlineStr">
         <is>
@@ -47022,8 +47500,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1481" t="n">
-        <v>0.18</v>
+      <c r="D1481" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1481" t="inlineStr">
         <is>
@@ -47052,8 +47532,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1482" t="n">
-        <v>0.18</v>
+      <c r="D1482" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1482" t="inlineStr">
         <is>
@@ -47082,8 +47564,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1483" t="n">
-        <v>0.18</v>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1483" t="inlineStr">
         <is>
@@ -47976,8 +48460,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1511" t="n">
-        <v>0.18</v>
+      <c r="D1511" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1511" t="inlineStr">
         <is>
@@ -48006,8 +48492,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1512" t="n">
-        <v>0.2</v>
+      <c r="D1512" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
       </c>
       <c r="E1512" t="inlineStr">
         <is>
@@ -48036,8 +48524,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1513" t="n">
-        <v>0.2</v>
+      <c r="D1513" t="inlineStr">
+        <is>
+          <t>0,20</t>
+        </is>
       </c>
       <c r="E1513" t="inlineStr">
         <is>
@@ -48066,8 +48556,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1514" t="n">
-        <v>0.18</v>
+      <c r="D1514" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1514" t="inlineStr">
         <is>
@@ -48096,8 +48588,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1515" t="n">
-        <v>0.18</v>
+      <c r="D1515" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1515" t="inlineStr">
         <is>
@@ -48126,8 +48620,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1516" t="n">
-        <v>0.18</v>
+      <c r="D1516" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1516" t="inlineStr">
         <is>
@@ -48156,8 +48652,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1517" t="n">
-        <v>0.18</v>
+      <c r="D1517" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1517" t="inlineStr">
         <is>
@@ -49306,8 +49804,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1553" t="n">
-        <v>0.18</v>
+      <c r="D1553" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1553" t="inlineStr">
         <is>
@@ -49336,8 +49836,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1554" t="n">
-        <v>0.18</v>
+      <c r="D1554" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1554" t="inlineStr">
         <is>
@@ -49366,8 +49868,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1555" t="n">
-        <v>0.18</v>
+      <c r="D1555" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1555" t="inlineStr">
         <is>
@@ -49396,8 +49900,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1556" t="n">
-        <v>0.18</v>
+      <c r="D1556" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1556" t="inlineStr">
         <is>
@@ -49426,8 +49932,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1557" t="n">
-        <v>0.18</v>
+      <c r="D1557" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1557" t="inlineStr">
         <is>
@@ -49456,8 +49964,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1558" t="n">
-        <v>0.18</v>
+      <c r="D1558" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1558" t="inlineStr">
         <is>
@@ -49486,8 +49996,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1559" t="n">
-        <v>0.18</v>
+      <c r="D1559" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1559" t="inlineStr">
         <is>
@@ -49516,8 +50028,10 @@
           <t>METRONIDAZOL</t>
         </is>
       </c>
-      <c r="D1560" t="n">
-        <v>2.5</v>
+      <c r="D1560" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
       </c>
       <c r="E1560" t="inlineStr">
         <is>
@@ -49546,8 +50060,10 @@
           <t>METRONIDAZOL</t>
         </is>
       </c>
-      <c r="D1561" t="n">
-        <v>2.5</v>
+      <c r="D1561" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
       </c>
       <c r="E1561" t="inlineStr">
         <is>
@@ -49576,8 +50092,10 @@
           <t>METRONIDAZOL</t>
         </is>
       </c>
-      <c r="D1562" t="n">
-        <v>2.5</v>
+      <c r="D1562" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
       </c>
       <c r="E1562" t="inlineStr">
         <is>
@@ -49606,8 +50124,10 @@
           <t>METRONIDAZOL</t>
         </is>
       </c>
-      <c r="D1563" t="n">
-        <v>2.5</v>
+      <c r="D1563" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
       </c>
       <c r="E1563" t="inlineStr">
         <is>
@@ -49636,8 +50156,10 @@
           <t>METRONIDAZOL</t>
         </is>
       </c>
-      <c r="D1564" t="n">
-        <v>2.5</v>
+      <c r="D1564" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
       </c>
       <c r="E1564" t="inlineStr">
         <is>
@@ -50338,8 +50860,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1586" t="n">
-        <v>0.18</v>
+      <c r="D1586" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1586" t="inlineStr">
         <is>
@@ -50368,8 +50892,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1587" t="n">
-        <v>0.18</v>
+      <c r="D1587" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1587" t="inlineStr">
         <is>
@@ -50398,8 +50924,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1588" t="n">
-        <v>0.18</v>
+      <c r="D1588" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1588" t="inlineStr">
         <is>
@@ -50428,8 +50956,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1589" t="n">
-        <v>0.2</v>
+      <c r="D1589" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
       </c>
       <c r="E1589" t="inlineStr">
         <is>
@@ -50458,8 +50988,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1590" t="n">
-        <v>0.18</v>
+      <c r="D1590" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1590" t="inlineStr">
         <is>
@@ -50488,8 +51020,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1591" t="n">
-        <v>0.18</v>
+      <c r="D1591" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1591" t="inlineStr">
         <is>
@@ -50518,8 +51052,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1592" t="n">
-        <v>0.2</v>
+      <c r="D1592" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
       </c>
       <c r="E1592" t="inlineStr">
         <is>
@@ -50548,8 +51084,10 @@
           <t>METRONIDAZOL</t>
         </is>
       </c>
-      <c r="D1593" t="n">
-        <v>2.5</v>
+      <c r="D1593" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
       </c>
       <c r="E1593" t="inlineStr">
         <is>
@@ -50578,8 +51116,10 @@
           <t>METRONIDAZOL</t>
         </is>
       </c>
-      <c r="D1594" t="n">
-        <v>2.5</v>
+      <c r="D1594" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
       </c>
       <c r="E1594" t="inlineStr">
         <is>
@@ -50608,8 +51148,10 @@
           <t>METRONIDAZOL</t>
         </is>
       </c>
-      <c r="D1595" t="n">
-        <v>2.5</v>
+      <c r="D1595" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
       </c>
       <c r="E1595" t="inlineStr">
         <is>
@@ -50638,8 +51180,10 @@
           <t>METRONIDAZOL</t>
         </is>
       </c>
-      <c r="D1596" t="n">
-        <v>2.5</v>
+      <c r="D1596" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
       </c>
       <c r="E1596" t="inlineStr">
         <is>
@@ -50668,8 +51212,10 @@
           <t>METRONIDAZOL</t>
         </is>
       </c>
-      <c r="D1597" t="n">
-        <v>2.5</v>
+      <c r="D1597" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
       </c>
       <c r="E1597" t="inlineStr">
         <is>
@@ -51754,8 +52300,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1631" t="n">
-        <v>0.18</v>
+      <c r="D1631" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1631" t="inlineStr">
         <is>
@@ -51784,8 +52332,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1632" t="n">
-        <v>0.18</v>
+      <c r="D1632" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1632" t="inlineStr">
         <is>
@@ -51814,8 +52364,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1633" t="n">
-        <v>0.18</v>
+      <c r="D1633" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1633" t="inlineStr">
         <is>
@@ -51844,8 +52396,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1634" t="n">
-        <v>0.2</v>
+      <c r="D1634" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
       </c>
       <c r="E1634" t="inlineStr">
         <is>
@@ -51874,8 +52428,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1635" t="n">
-        <v>0.2</v>
+      <c r="D1635" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
       </c>
       <c r="E1635" t="inlineStr">
         <is>
@@ -51904,8 +52460,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1636" t="n">
-        <v>0.18</v>
+      <c r="D1636" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1636" t="inlineStr">
         <is>
@@ -51934,8 +52492,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1637" t="n">
-        <v>0.2</v>
+      <c r="D1637" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
       </c>
       <c r="E1637" t="inlineStr">
         <is>
@@ -52600,8 +53160,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1658" t="n">
-        <v>0.2</v>
+      <c r="D1658" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
       </c>
       <c r="E1658" t="inlineStr">
         <is>
@@ -52630,8 +53192,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1659" t="n">
-        <v>0.2</v>
+      <c r="D1659" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
       </c>
       <c r="E1659" t="inlineStr">
         <is>
@@ -52660,8 +53224,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1660" t="n">
-        <v>0.18</v>
+      <c r="D1660" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
       </c>
       <c r="E1660" t="inlineStr">
         <is>
@@ -52690,8 +53256,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1661" t="n">
-        <v>0.2</v>
+      <c r="D1661" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
       </c>
       <c r="E1661" t="inlineStr">
         <is>
@@ -52720,8 +53288,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1662" t="n">
-        <v>0.2</v>
+      <c r="D1662" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
       </c>
       <c r="E1662" t="inlineStr">
         <is>
@@ -52750,8 +53320,10 @@
           <t>CANINSULIN</t>
         </is>
       </c>
-      <c r="D1663" t="n">
-        <v>0.2</v>
+      <c r="D1663" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
       </c>
       <c r="E1663" t="inlineStr">
         <is>
@@ -52872,8 +53444,10 @@
           <t>METRONIDAZOL</t>
         </is>
       </c>
-      <c r="D1667" t="n">
-        <v>2.5</v>
+      <c r="D1667" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
       </c>
       <c r="E1667" t="inlineStr">
         <is>
@@ -52883,6 +53457,2834 @@
       <c r="F1667" t="inlineStr">
         <is>
           <t>orig38</t>
+        </is>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1668" t="inlineStr">
+        <is>
+          <t>DIPIRONA</t>
+        </is>
+      </c>
+      <c r="D1668" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1668" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1668" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1669" t="inlineStr">
+        <is>
+          <t>CANINSULIN</t>
+        </is>
+      </c>
+      <c r="D1669" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="E1669" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1669" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1670" t="inlineStr">
+        <is>
+          <t>TRILOSTANO</t>
+        </is>
+      </c>
+      <c r="D1670" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="E1670" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1670" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1671" t="inlineStr">
+        <is>
+          <t>SILIMARINA</t>
+        </is>
+      </c>
+      <c r="D1671" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1671" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1671" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1672" t="inlineStr">
+        <is>
+          <t>FENOFIBRATO</t>
+        </is>
+      </c>
+      <c r="D1672" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1672" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1672" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1673" t="inlineStr">
+        <is>
+          <t>BILETAN_ENZIMATICO</t>
+        </is>
+      </c>
+      <c r="D1673" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="E1673" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1673" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1674" t="inlineStr">
+        <is>
+          <t>PSYLLIUM</t>
+        </is>
+      </c>
+      <c r="D1674" t="inlineStr"/>
+      <c r="E1674" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1674" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>ayuno</t>
+        </is>
+      </c>
+      <c r="C1675" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="D1675" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1675" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1675" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1676" t="inlineStr">
+        <is>
+          <t>TRILOSTANO</t>
+        </is>
+      </c>
+      <c r="D1676" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="E1676" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1676" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>SILIMARINA</t>
+        </is>
+      </c>
+      <c r="D1677" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1677" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1677" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1678" t="inlineStr">
+        <is>
+          <t>FENOFIBRATO</t>
+        </is>
+      </c>
+      <c r="D1678" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1678" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1678" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1679" t="inlineStr">
+        <is>
+          <t>CANINSULIN</t>
+        </is>
+      </c>
+      <c r="D1679" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="E1679" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1679" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1680" t="inlineStr">
+        <is>
+          <t>DIPIRONA</t>
+        </is>
+      </c>
+      <c r="D1680" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1680" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1680" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1681" t="inlineStr">
+        <is>
+          <t>PSYLLIUM</t>
+        </is>
+      </c>
+      <c r="D1681" t="inlineStr"/>
+      <c r="E1681" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1681" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1682" t="inlineStr">
+        <is>
+          <t>TRILOSTANO</t>
+        </is>
+      </c>
+      <c r="D1682" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="E1682" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1682" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>SILIMARINA</t>
+        </is>
+      </c>
+      <c r="D1683" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1683" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1683" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1684" t="inlineStr">
+        <is>
+          <t>FENOFIBRATO</t>
+        </is>
+      </c>
+      <c r="D1684" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1684" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1684" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1685" t="inlineStr">
+        <is>
+          <t>CANINSULIN</t>
+        </is>
+      </c>
+      <c r="D1685" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="E1685" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1685" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1686" t="inlineStr">
+        <is>
+          <t>DIPIRONA</t>
+        </is>
+      </c>
+      <c r="D1686" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1686" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1686" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1687" t="inlineStr">
+        <is>
+          <t>PSYLLIUM</t>
+        </is>
+      </c>
+      <c r="D1687" t="inlineStr"/>
+      <c r="E1687" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1687" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>ayuno</t>
+        </is>
+      </c>
+      <c r="C1688" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="D1688" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1688" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1688" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1689" t="inlineStr">
+        <is>
+          <t>TRILOSTANO</t>
+        </is>
+      </c>
+      <c r="D1689" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="E1689" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1689" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1690" t="inlineStr">
+        <is>
+          <t>SILIMARINA</t>
+        </is>
+      </c>
+      <c r="D1690" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1690" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1690" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1691" t="inlineStr">
+        <is>
+          <t>FENOFIBRATO</t>
+        </is>
+      </c>
+      <c r="D1691" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1691" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1691" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1692" t="inlineStr">
+        <is>
+          <t>CANINSULIN</t>
+        </is>
+      </c>
+      <c r="D1692" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="E1692" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1692" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1693" t="inlineStr">
+        <is>
+          <t>DIPIRONA</t>
+        </is>
+      </c>
+      <c r="D1693" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1693" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1693" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1694" t="inlineStr">
+        <is>
+          <t>PSYLLIUM</t>
+        </is>
+      </c>
+      <c r="D1694" t="inlineStr"/>
+      <c r="E1694" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1694" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1695" t="inlineStr">
+        <is>
+          <t>TRILOSTANO</t>
+        </is>
+      </c>
+      <c r="D1695" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="E1695" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1695" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1696" t="inlineStr">
+        <is>
+          <t>SILIMARINA</t>
+        </is>
+      </c>
+      <c r="D1696" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1696" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1696" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1697" t="inlineStr">
+        <is>
+          <t>FENOFIBRATO</t>
+        </is>
+      </c>
+      <c r="D1697" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1697" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1697" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1698" t="inlineStr">
+        <is>
+          <t>CANINSULIN</t>
+        </is>
+      </c>
+      <c r="D1698" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="E1698" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1698" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1699" t="inlineStr">
+        <is>
+          <t>DIPIRONA</t>
+        </is>
+      </c>
+      <c r="D1699" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1699" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1699" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1700" t="inlineStr">
+        <is>
+          <t>PSYLLIUM</t>
+        </is>
+      </c>
+      <c r="D1700" t="inlineStr"/>
+      <c r="E1700" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1700" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>ayuno</t>
+        </is>
+      </c>
+      <c r="C1701" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="D1701" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1701" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1701" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1702" t="inlineStr">
+        <is>
+          <t>TRILOSTANO</t>
+        </is>
+      </c>
+      <c r="D1702" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="E1702" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1702" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1703" t="inlineStr">
+        <is>
+          <t>SILIMARINA</t>
+        </is>
+      </c>
+      <c r="D1703" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1703" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1703" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1704" t="inlineStr">
+        <is>
+          <t>FENOFIBRATO</t>
+        </is>
+      </c>
+      <c r="D1704" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1704" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1704" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1705" t="inlineStr">
+        <is>
+          <t>CANINSULIN</t>
+        </is>
+      </c>
+      <c r="D1705" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="E1705" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1705" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1706" t="inlineStr">
+        <is>
+          <t>DIPIRONA</t>
+        </is>
+      </c>
+      <c r="D1706" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1706" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1706" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1707" t="inlineStr">
+        <is>
+          <t>PSYLLIUM</t>
+        </is>
+      </c>
+      <c r="D1707" t="inlineStr"/>
+      <c r="E1707" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1707" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1708" t="inlineStr">
+        <is>
+          <t>TRILOSTANO</t>
+        </is>
+      </c>
+      <c r="D1708" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="E1708" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1708" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1709" t="inlineStr">
+        <is>
+          <t>SILIMARINA</t>
+        </is>
+      </c>
+      <c r="D1709" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1709" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1709" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1710" t="inlineStr">
+        <is>
+          <t>FENOFIBRATO</t>
+        </is>
+      </c>
+      <c r="D1710" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1710" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1710" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1711" t="inlineStr">
+        <is>
+          <t>CANINSULIN</t>
+        </is>
+      </c>
+      <c r="D1711" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="E1711" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1711" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1712" t="inlineStr">
+        <is>
+          <t>DIPIRONA</t>
+        </is>
+      </c>
+      <c r="D1712" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1712" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1712" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1713" t="inlineStr">
+        <is>
+          <t>PSYLLIUM</t>
+        </is>
+      </c>
+      <c r="D1713" t="inlineStr"/>
+      <c r="E1713" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1713" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>ayuno</t>
+        </is>
+      </c>
+      <c r="C1714" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="D1714" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1714" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1714" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1715" t="inlineStr">
+        <is>
+          <t>TRILOSTANO</t>
+        </is>
+      </c>
+      <c r="D1715" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="E1715" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1715" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1716" t="inlineStr">
+        <is>
+          <t>SILIMARINA</t>
+        </is>
+      </c>
+      <c r="D1716" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1716" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1716" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1717" t="inlineStr">
+        <is>
+          <t>FENOFIBRATO</t>
+        </is>
+      </c>
+      <c r="D1717" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1717" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1717" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1718" t="inlineStr">
+        <is>
+          <t>CANINSULIN</t>
+        </is>
+      </c>
+      <c r="D1718" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="E1718" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1718" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1719" t="inlineStr">
+        <is>
+          <t>DIPIRONA</t>
+        </is>
+      </c>
+      <c r="D1719" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1719" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1719" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1720" t="inlineStr">
+        <is>
+          <t>PSYLLIUM</t>
+        </is>
+      </c>
+      <c r="D1720" t="inlineStr"/>
+      <c r="E1720" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1720" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1721" t="inlineStr">
+        <is>
+          <t>TRILOSTANO</t>
+        </is>
+      </c>
+      <c r="D1721" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="E1721" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1721" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1722" t="inlineStr">
+        <is>
+          <t>SILIMARINA</t>
+        </is>
+      </c>
+      <c r="D1722" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1722" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1722" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1723" t="inlineStr">
+        <is>
+          <t>FENOFIBRATO</t>
+        </is>
+      </c>
+      <c r="D1723" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1723" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1723" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1724" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1724" t="inlineStr">
+        <is>
+          <t>CANINSULIN</t>
+        </is>
+      </c>
+      <c r="D1724" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="E1724" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1724" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1725" t="inlineStr">
+        <is>
+          <t>DIPIRONA</t>
+        </is>
+      </c>
+      <c r="D1725" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1725" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1725" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1726" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1726" t="inlineStr">
+        <is>
+          <t>PSYLLIUM</t>
+        </is>
+      </c>
+      <c r="D1726" t="inlineStr"/>
+      <c r="E1726" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1726" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>ayuno</t>
+        </is>
+      </c>
+      <c r="C1727" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="D1727" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1727" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1727" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1728" t="inlineStr">
+        <is>
+          <t>TRILOSTANO</t>
+        </is>
+      </c>
+      <c r="D1728" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="E1728" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1728" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1729" t="inlineStr">
+        <is>
+          <t>SILIMARINA</t>
+        </is>
+      </c>
+      <c r="D1729" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1729" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1729" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1730" t="inlineStr">
+        <is>
+          <t>FENOFIBRATO</t>
+        </is>
+      </c>
+      <c r="D1730" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1730" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1730" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1731" t="inlineStr">
+        <is>
+          <t>CANINSULIN</t>
+        </is>
+      </c>
+      <c r="D1731" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="E1731" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1731" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1732" t="inlineStr">
+        <is>
+          <t>DIPIRONA</t>
+        </is>
+      </c>
+      <c r="D1732" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1732" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1732" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1733" t="inlineStr">
+        <is>
+          <t>PSYLLIUM</t>
+        </is>
+      </c>
+      <c r="D1733" t="inlineStr"/>
+      <c r="E1733" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1733" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1734" t="inlineStr">
+        <is>
+          <t>TRILOSTANO</t>
+        </is>
+      </c>
+      <c r="D1734" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="E1734" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1734" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1735" t="inlineStr">
+        <is>
+          <t>SILIMARINA</t>
+        </is>
+      </c>
+      <c r="D1735" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1735" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1735" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1736" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1736" t="inlineStr">
+        <is>
+          <t>FENOFIBRATO</t>
+        </is>
+      </c>
+      <c r="D1736" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1736" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1736" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1737" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1737" t="inlineStr">
+        <is>
+          <t>CANINSULIN</t>
+        </is>
+      </c>
+      <c r="D1737" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="E1737" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1737" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1738" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1738" t="inlineStr">
+        <is>
+          <t>DIPIRONA</t>
+        </is>
+      </c>
+      <c r="D1738" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1738" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1738" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1739" t="inlineStr">
+        <is>
+          <t>PSYLLIUM</t>
+        </is>
+      </c>
+      <c r="D1739" t="inlineStr"/>
+      <c r="E1739" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1739" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>ayuno</t>
+        </is>
+      </c>
+      <c r="C1740" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="D1740" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1740" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1740" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1741" t="inlineStr">
+        <is>
+          <t>TRILOSTANO</t>
+        </is>
+      </c>
+      <c r="D1741" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="E1741" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1741" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1742" t="inlineStr">
+        <is>
+          <t>SILIMARINA</t>
+        </is>
+      </c>
+      <c r="D1742" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1742" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1742" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1743" t="inlineStr">
+        <is>
+          <t>FENOFIBRATO</t>
+        </is>
+      </c>
+      <c r="D1743" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1743" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1743" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1744" t="inlineStr">
+        <is>
+          <t>CANINSULIN</t>
+        </is>
+      </c>
+      <c r="D1744" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="E1744" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1744" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1745" t="inlineStr">
+        <is>
+          <t>DIPIRONA</t>
+        </is>
+      </c>
+      <c r="D1745" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1745" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1745" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1746" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1746" t="inlineStr">
+        <is>
+          <t>PSYLLIUM</t>
+        </is>
+      </c>
+      <c r="D1746" t="inlineStr"/>
+      <c r="E1746" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1746" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1747" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1747" t="inlineStr">
+        <is>
+          <t>TRILOSTANO</t>
+        </is>
+      </c>
+      <c r="D1747" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="E1747" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1747" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1748" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1748" t="inlineStr">
+        <is>
+          <t>SILIMARINA</t>
+        </is>
+      </c>
+      <c r="D1748" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1748" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1748" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1749" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1749" t="inlineStr">
+        <is>
+          <t>FENOFIBRATO</t>
+        </is>
+      </c>
+      <c r="D1749" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1749" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1749" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1750" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1750" t="inlineStr">
+        <is>
+          <t>CANINSULIN</t>
+        </is>
+      </c>
+      <c r="D1750" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="E1750" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1750" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1751" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1751" t="inlineStr">
+        <is>
+          <t>DIPIRONA</t>
+        </is>
+      </c>
+      <c r="D1751" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E1751" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1751" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1752" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1752" t="inlineStr">
+        <is>
+          <t>PSYLLIUM</t>
+        </is>
+      </c>
+      <c r="D1752" t="inlineStr"/>
+      <c r="E1752" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1752" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1753" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1753" t="inlineStr">
+        <is>
+          <t>BILETAN_ENZIMATICO</t>
+        </is>
+      </c>
+      <c r="D1753" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="E1753" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1753" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1754" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1754" t="inlineStr">
+        <is>
+          <t>BILETAN_ENZIMATICO</t>
+        </is>
+      </c>
+      <c r="D1754" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="E1754" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1754" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1755" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1755" t="inlineStr">
+        <is>
+          <t>BILETAN_ENZIMATICO</t>
+        </is>
+      </c>
+      <c r="D1755" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="E1755" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1755" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1756" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1756" t="inlineStr">
+        <is>
+          <t>BILETAN_ENZIMATICO</t>
+        </is>
+      </c>
+      <c r="D1756" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="E1756" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1756" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1757" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1757" t="inlineStr">
+        <is>
+          <t>BILETAN_ENZIMATICO</t>
+        </is>
+      </c>
+      <c r="D1757" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="E1757" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1757" t="inlineStr">
+        <is>
+          <t>usuario</t>
         </is>
       </c>
     </row>
